--- a/data/maintainer/Verlog.xlsx
+++ b/data/maintainer/Verlog.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A135"/>
+  <dimension ref="A1:A148"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="171.125" customWidth="1" style="9" min="1" max="1"/>
@@ -1105,6 +1105,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1119,6 +1120,8 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
@@ -1133,6 +1136,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -1168,6 +1173,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
@@ -1182,6 +1188,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
@@ -1203,6 +1210,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -1224,6 +1232,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
@@ -1238,6 +1247,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
@@ -1259,6 +1269,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -1273,6 +1284,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
@@ -1294,6 +1306,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
@@ -1329,6 +1342,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
@@ -1371,6 +1385,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
@@ -1413,6 +1428,7 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
@@ -1427,6 +1443,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65" customFormat="1" s="12">
       <c r="A65" s="11" t="inlineStr">
         <is>
@@ -1441,6 +1458,7 @@
         </is>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
@@ -1462,6 +1480,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72" customFormat="1" s="12">
       <c r="A72" s="11" t="inlineStr">
         <is>
@@ -1504,6 +1523,7 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
@@ -1532,6 +1552,7 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84" customFormat="1" s="12">
       <c r="A84" s="13" t="inlineStr">
         <is>
@@ -1623,6 +1644,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
@@ -1721,6 +1743,7 @@
         </is>
       </c>
     </row>
+    <row r="112"/>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
@@ -1798,6 +1821,7 @@
         </is>
       </c>
     </row>
+    <row r="124"/>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
@@ -1871,6 +1895,79 @@
         </is>
       </c>
     </row>
+    <row r="136"/>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>v26.10.2（20261009）</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1.一条龙链路加固：高危单链节点补 on_error 逃生——PVP免费票确认（FreeNO/FreeYes）、广场跳转镜中之战、快速狩猎金币/史莱姆确认（GoldHunt/SlimeHunt）等易识别失败节点，识别超时不再让后续PVP/狩猎/背包/赛季整串跳过，而是自动回主菜单继续下一段；</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2.广场女神像链路修复：Loading_Square 识别区域收紧，加载结束后新增多候选逃生尾缀；新增经营管理「餐厅加载」识别节点（RestaurantLoading_1），避免加载页被误判；</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>3.识别精度调优：PVP / 赛季活动多处模板阈值、max_hit 与 timeout 调整，降低误匹配与超时红字概率；</t>
+        </is>
+      </c>
+    </row>
+    <row r="141"/>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>v26.10.3（20261010）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1.日常收菜链路拆分：公会低保、经营管理+小屋、广场女神像拆成三条独立链路（对应新增 Sociaty / Operate / Square 三份管线），「一条龙日常」新增后两段入口；任一段识别失败只跳过该段，不再连累后面PVP/狩猎/背包/赛季整串；</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2.每日跑商「高价卖出」重做：新增商店「价目表」读取与商品旁 120% 峰值标记识别（Sale120Marker 重新标定），只挑高价物品卖出；买完或商品售罄自动接上卖出环节，卖完自动回主城收尾（跑商组件 agent/trader.exe 同步升级）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>3.「重建商店收藏清单」新增主城终结算子（OCR「付费商店」），回到主城时干净收尾，不再空转到超时；</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>4.料理链路加固：新增候选节点与重试上限、等待超时放宽到 12 秒，餐厅加载慢也不再中断「做料理再卖出」这一步；</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>5.稳定性细节：末日之书选卡与「滑到N级装备」补重试上限、资源吸收新增选择卡/经营管理兜底节点，识别偶发失败不再卡住；</t>
+        </is>
+      </c>
+    </row>
+    <row r="148"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/data/maintainer/Verlog.xlsx
+++ b/data/maintainer/Verlog.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A148"/>
+  <dimension ref="A1:A158"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="171.125" customWidth="1" style="9" min="1" max="1"/>
@@ -1897,28 +1897,28 @@
     </row>
     <row r="136"/>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>v26.10.2（20261009）</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t>1.一条龙链路加固：高危单链节点补 on_error 逃生——PVP免费票确认（FreeNO/FreeYes）、广场跳转镜中之战、快速狩猎金币/史莱姆确认（GoldHunt/SlimeHunt）等易识别失败节点，识别超时不再让后续PVP/狩猎/背包/赛季整串跳过，而是自动回主菜单继续下一段；</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>2.广场女神像链路修复：Loading_Square 识别区域收紧，加载结束后新增多候选逃生尾缀；新增经营管理「餐厅加载」识别节点（RestaurantLoading_1），避免加载页被误判；</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>3.识别精度调优：PVP / 赛季活动多处模板阈值、max_hit 与 timeout 调整，降低误匹配与超时红字概率；</t>
         </is>
@@ -1926,48 +1926,112 @@
     </row>
     <row r="141"/>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>v26.10.3（20261010）</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>1.日常收菜链路拆分：公会低保、经营管理+小屋、广场女神像拆成三条独立链路（对应新增 Sociaty / Operate / Square 三份管线），「一条龙日常」新增后两段入口；任一段识别失败只跳过该段，不再连累后面PVP/狩猎/背包/赛季整串；</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>2.每日跑商「高价卖出」重做：新增商店「价目表」读取与商品旁 120% 峰值标记识别（Sale120Marker 重新标定），只挑高价物品卖出；买完或商品售罄自动接上卖出环节，卖完自动回主城收尾（跑商组件 agent/trader.exe 同步升级）；</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>3.「重建商店收藏清单」新增主城终结算子（OCR「付费商店」），回到主城时干净收尾，不再空转到超时；</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t>4.料理链路加固：新增候选节点与重试上限、等待超时放宽到 12 秒，餐厅加载慢也不再中断「做料理再卖出」这一步；</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="3" t="inlineStr">
         <is>
           <t>5.稳定性细节：末日之书选卡与「滑到N级装备」补重试上限、资源吸收新增选择卡/经营管理兜底节点，识别偶发失败不再卡住；</t>
         </is>
       </c>
     </row>
     <row r="148"/>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>v26.10.4（20261012）</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1.星期/日程门控改为「连查两次」：资源吸收（首轮卡、次轮卡）、魔兽商店、每周任务、跑商料理门控的 ScheduleRecognition 由单次判定改为连续两次，一次偶发识别失败不再让当天任务整个跳过；</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2.每周任务新增空节点 WeeklyTask_End：门控两次都不命中时落到空节点绿色结束，不再走死端空转到超时；</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>3.跑商料理门控兜底：不制作料理时若两次门控都不命中，改为直接进入高价卖出（SellPremium_Start），不再结束整个跑商任务；</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>4.砍价按钮识别由模板匹配改为 OCR：跑商「跳过砍价进入商店页」、「重建商店收藏清单」的砍价入口与回主城判定的 bargain 模板改为 OCR 识别「砍/价/选/择」（小框 roi [104,607,43,40]），不再受大框模板阈值偏低导致的误判影响；</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>5.快速狩猎识别修正：「MAX」按钮 ROI 由 80×80 收紧到 39×17、阈值下调；三个「快速狩猎」OCR 去掉错词「快速狩」并去掉自引用循环，命中后直接进设置次数；</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>6.启动游戏：「7天内不再显示」弹窗 OCR 改为拆词匹配、阈值下调，勾选更容易命中；</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>7.文案：一条龙日常「开启自动战斗」选项明确为「赛季活动战斗关卡—请选择是否使用自动战斗推关」；</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>8.维护侧（不影响使用）：退役「维护版每日备份」方案——夸克客户端取消开机自启后备份链断裂，实测该方案从未成功产出备份，相关脚本与计划任务一并删除，设计与复活清单归档在 maintainer/legacy/备份方案退役说明.md；</t>
+        </is>
+      </c>
+    </row>
+    <row r="158"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/data/maintainer/Verlog.xlsx
+++ b/data/maintainer/Verlog.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A158"/>
+  <dimension ref="A1:A168"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="171.125" customWidth="1" style="9" min="1" max="1"/>
@@ -1105,7 +1105,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1120,8 +1119,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
@@ -1136,8 +1133,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -1173,7 +1168,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
@@ -1188,7 +1182,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
@@ -1210,7 +1203,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -1232,7 +1224,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
@@ -1247,7 +1238,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
@@ -1269,7 +1259,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -1284,7 +1273,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
@@ -1306,7 +1294,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
@@ -1342,7 +1329,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
@@ -1385,7 +1371,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
@@ -1428,7 +1413,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
@@ -1443,7 +1427,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65" customFormat="1" s="12">
       <c r="A65" s="11" t="inlineStr">
         <is>
@@ -1458,7 +1441,6 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
@@ -1480,7 +1462,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
     <row r="72" customFormat="1" s="12">
       <c r="A72" s="11" t="inlineStr">
         <is>
@@ -1523,7 +1504,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
@@ -1552,7 +1532,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84" customFormat="1" s="12">
       <c r="A84" s="13" t="inlineStr">
         <is>
@@ -1644,7 +1623,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
@@ -1743,7 +1721,6 @@
         </is>
       </c>
     </row>
-    <row r="112"/>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
@@ -1821,7 +1798,6 @@
         </is>
       </c>
     </row>
-    <row r="124"/>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
@@ -1895,7 +1871,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
@@ -1924,7 +1899,6 @@
         </is>
       </c>
     </row>
-    <row r="141"/>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
@@ -1967,71 +1941,139 @@
         </is>
       </c>
     </row>
-    <row r="148"/>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t>v26.10.4（20261012）</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>1.星期/日程门控改为「连查两次」：资源吸收（首轮卡、次轮卡）、魔兽商店、每周任务、跑商料理门控的 ScheduleRecognition 由单次判定改为连续两次，一次偶发识别失败不再让当天任务整个跳过；</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t>2.每周任务新增空节点 WeeklyTask_End：门控两次都不命中时落到空节点绿色结束，不再走死端空转到超时；</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t>3.跑商料理门控兜底：不制作料理时若两次门控都不命中，改为直接进入高价卖出（SellPremium_Start），不再结束整个跑商任务；</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t>4.砍价按钮识别由模板匹配改为 OCR：跑商「跳过砍价进入商店页」、「重建商店收藏清单」的砍价入口与回主城判定的 bargain 模板改为 OCR 识别「砍/价/选/择」（小框 roi [104,607,43,40]），不再受大框模板阈值偏低导致的误判影响；</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="3" t="inlineStr">
         <is>
           <t>5.快速狩猎识别修正：「MAX」按钮 ROI 由 80×80 收紧到 39×17、阈值下调；三个「快速狩猎」OCR 去掉错词「快速狩」并去掉自引用循环，命中后直接进设置次数；</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>6.启动游戏：「7天内不再显示」弹窗 OCR 改为拆词匹配、阈值下调，勾选更容易命中；</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t>7.文案：一条龙日常「开启自动战斗」选项明确为「赛季活动战斗关卡—请选择是否使用自动战斗推关」；</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>8.维护侧（不影响使用）：退役「维护版每日备份」方案——夸克客户端取消开机自启后备份链断裂，实测该方案从未成功产出备份，相关脚本与计划任务一并删除，设计与复活清单归档在 maintainer/legacy/备份方案退役说明.md；</t>
         </is>
       </c>
     </row>
-    <row r="158"/>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>v26.10.5（20261014）</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>1.赛季活动入口合并：EnterWarcraft + EnterWarcraft2 合并为 EnterWarcraft_W，OCR 期望词合并为「剧情/解锁/普通/战斗/魔兽/追踪者」、识别框统一为 [1020,340,220,250]，进入活动页更稳；</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>2.赛季活动「自动战斗」新增失败兜底：保持节点等待由 9 秒放宽到 15 秒，新增「自动战斗失败」节点——识别到失败会提示「赛季活动自动战斗失败，请手动挑战关卡」并返回活动主页，不再卡在战斗界面；</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>3.魔兽商店入口合并：EnterWarcraft_3 / _4 合并为 EnterWarcraft_WS；商店页识别拆成 InWarcraftShop_1 / _2 两个位置候选（roi 767,622,123,36 与 901,626,109,28），不同布局都能命中；</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>4.启动游戏加固：InShadow 重试上限 2→3、补 on_error 逃生与 4.5 秒超时；StartGame 入口顺序调整为先处理更新 / 公告 / 弹窗再进游戏；</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>5.广场女神像：GetSquare 重试上限 2→1，识别不到时改接 MoveSquare 走位；MoveSquare 等待 7.5 秒→9 秒；</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>6.快速狩猎：OreHunt / WoodHunt 补 post_delay 1.5 秒、repeat_delay 0.5→1.5 秒，滑动选择更稳；</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>7.跑商组件升级（agent/trader.exe）：商品名匹配支持 OCR 丢尾字（「胡萝」也能匹配「胡萝卜」，仅对中日韩文字生效，避免英文别名被误匹配）；卖出弹窗标题识别框按实测截图重新标定；「拥有 / 可购买」数量支持千分位逗号（如 1,940）；过滤 15×12 以下的小噪声识别框；</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>8.广场女神像补充调整：GetSquare 命中后等待 1.5 秒→3 秒；GetDaily2 的后续链简化（去掉自引用与走位兜底）；Loading_Square 与 StartSquare 的候选顺序调整，收菜判定更顺；</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>9.星期 / 日程门控改回「只查一次」：v26.10.4 曾把资源吸收（首轮 / 次轮）、每周任务、跑商料理门控改为连查两次，实测无必要，本版撤回为一次判定；每周任务保留 WeeklyTask_End 收尾空节点，不执行的日子仍绿色结束；</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/data/maintainer/Verlog.xlsx
+++ b/data/maintainer/Verlog.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A168"/>
+  <dimension ref="A1:A172"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="171.125" customWidth="1" style="9" min="1" max="1"/>
@@ -2061,16 +2061,40 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t>8.广场女神像补充调整：GetSquare 命中后等待 1.5 秒→3 秒；GetDaily2 的后续链简化（去掉自引用与走位兜底）；Loading_Square 与 StartSquare 的候选顺序调整，收菜判定更顺；</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>9.星期 / 日程门控改回「只查一次」：v26.10.4 曾把资源吸收（首轮 / 次轮）、每周任务、跑商料理门控改为连查两次，实测无必要，本版撤回为一次判定；每周任务保留 WeeklyTask_End 收尾空节点，不执行的日子仍绿色结束；</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>v26.10.6（20261014）</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1.启动游戏候选顺序调整：StartGame 的候选链里，「返回主城」的判断从「进入游戏」之后挪到「取消 / 拒绝奖励 / 拒绝公告 / 7 天内不再显示」之后——冷启动时先把更新提示、公告、各类弹窗清干净，再判断是否已经回到主城，减少被弹窗挡住后反复重试；</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2.剪影页处理加快：InShadow 识别等待由 4.5 秒缩短到 3 秒，冷启动判定更快；同时去掉累计命中上限（原 max_hit 3），避免同一局里多次进出剪影页后该节点被永久跳过、后续真正需要退出剪影时无人处理；</t>
         </is>
       </c>
     </row>

--- a/data/maintainer/Verlog.xlsx
+++ b/data/maintainer/Verlog.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A179"/>
+  <dimension ref="A1:A188"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="171.125" customWidth="1" style="9" min="1" max="1"/>
@@ -2099,47 +2099,106 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" s="3" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>v26.10.7（20261019）</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>1.Bag 一键分解（IntensifyChoose）新增 timeout + on_error 逃生：识别不到目标时不再红叉，改走启动链；</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t>2.Draw 抽卡跳过优化：DrawSkip 连跳到跳过按钮消失、新增阈值、DrawGoBack 回插 DrawSkip、AllDrawSure 后延迟 1.5s→3s；</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="3" t="inlineStr">
         <is>
           <t>3.Trade/CookMeals 料理识别优化：Cook_dish_01~15 的 roi 统一为 [480,80,700,600]（原各 100×100 小框）、dish_08 阈值 0.7→0.8、Ccok_Swipe 后延迟 2s→3s、Coooooooook OCR 由「料/理」两字改为整词「料理」；</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>4.维护脚本（日志瘦身）路径 / 进程名 / 日志名随改名同步：maintainer/→data/maintainer/tools/、mxu.exe→MaaBd2.exe、maa.log→maafw.log；</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t>5.本版合并自本地 trae/Android 分支，已剔除 Trae 内部文档 .trae/（含本机路径，不入仓）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>v26.10.8（20261022）</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1.8 个进关卡节点统一加固：EnterOperating / EnterOperating_2 / EnterOperating_3 / EnterOperating_EC / EnterOperating_WM / AutoFishingEnter_1 / Cook_EnterOperating / SP_EnterOperating 的 max_hit 2→3、pre_delay 1.5s→3s（AutoFishing 1s→3s）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2.StartGame EnterGame post_delay 3s→6s（剪影页退出后多等 3s）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>3.WarcraftShop 加固：EnterWarcraft_WS post_delay 2s→6s、next 增加自身重试；InWarcraftShop_1/2 增加绝对坐标 target (824,640) / (952,640) + post_delay 3s；LeftGold_MS target_offset [23,18]→[29,37,-77,-124]（收敛为模板内 1×1 定点）、阈值 0.93→0.9；LeftRefinedDust_MS target_offset [25,28]→[24,37,-73,-125]；RefinedCrystal_MS 阈值 0.8→0.7；WarcraftShopBuyLoop post_delay 0.5s→2s；</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>4.Draw EnterDraw 新增 max_hit 3，next 尾部新增 [JumpBack]RejectAward / [JumpBack]RejectAnnouncement / [JumpBack]SevenDays（复用 StartGame 已有的弹窗清理节点，插在 Equipment 之后、StartGame 之前）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>5.RewardRoutine 新增 GetAllrewards2：OCR「全部解锁/全部/解锁」roi [562,490,78,26] → Click，repeat 2、post_delay 4500、timeout 10000，挂在「检测感叹号」next 尾部（最低优先级）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>6.WeeklyTasks 的 WeeklyTask_End 位置调整（空节点，语义不变）；其余 diff 为 MPE 编辑器元数据（lastSyncTime / savedViewport / 节点坐标 / MPE version v2.0.6→v2.1.0），不影响运行；</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>7.已知遗留：EnterWarcraft_WS 的自引用重试未设 max_hit（进店失败时可能长时间重试），观察后续版本处理。</t>
         </is>
       </c>
     </row>

--- a/data/maintainer/Verlog.xlsx
+++ b/data/maintainer/Verlog.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A188"/>
+  <dimension ref="A1:A195"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="171.125" customWidth="1" style="9" min="1" max="1"/>
@@ -2144,61 +2144,106 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
+      <c r="A180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>v26.10.8（20261022）</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>1.8 个进关卡节点统一加固：EnterOperating / EnterOperating_2 / EnterOperating_3 / EnterOperating_EC / EnterOperating_WM / AutoFishingEnter_1 / Cook_EnterOperating / SP_EnterOperating 的 max_hit 2→3、pre_delay 1.5s→3s（AutoFishing 1s→3s）；</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>2.StartGame EnterGame post_delay 3s→6s（剪影页退出后多等 3s）；</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>3.WarcraftShop 加固：EnterWarcraft_WS post_delay 2s→6s、next 增加自身重试；InWarcraftShop_1/2 增加绝对坐标 target (824,640) / (952,640) + post_delay 3s；LeftGold_MS target_offset [23,18]→[29,37,-77,-124]（收敛为模板内 1×1 定点）、阈值 0.93→0.9；LeftRefinedDust_MS target_offset [25,28]→[24,37,-73,-125]；RefinedCrystal_MS 阈值 0.8→0.7；WarcraftShopBuyLoop post_delay 0.5s→2s；</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="3" t="inlineStr">
         <is>
           <t>4.Draw EnterDraw 新增 max_hit 3，next 尾部新增 [JumpBack]RejectAward / [JumpBack]RejectAnnouncement / [JumpBack]SevenDays（复用 StartGame 已有的弹窗清理节点，插在 Equipment 之后、StartGame 之前）；</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>5.RewardRoutine 新增 GetAllrewards2：OCR「全部解锁/全部/解锁」roi [562,490,78,26] → Click，repeat 2、post_delay 4500、timeout 10000，挂在「检测感叹号」next 尾部（最低优先级）；</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t>6.WeeklyTasks 的 WeeklyTask_End 位置调整（空节点，语义不变）；其余 diff 为 MPE 编辑器元数据（lastSyncTime / savedViewport / 节点坐标 / MPE version v2.0.6→v2.1.0），不影响运行；</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="3" t="inlineStr">
         <is>
           <t>7.已知遗留：EnterWarcraft_WS 的自引用重试未设 max_hit（进店失败时可能长时间重试），观察后续版本处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>v26.10.9（20261025）</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1.Draw EnterDraw 的 next 顺序调整：3 个弹窗清理节点 [JumpBack]RejectAward / [JumpBack]RejectAnnouncement / [JumpBack]SevenDays 从尾部提到最前面（原排在 Equipment 之后），抽卡页先清弹窗再点「抽抽乐」；</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2.Trade/RebuildTradeFavorites_Entry 入口拆分：「招募情况」RTF_OnSquare 拆为 RTF_OnSquare_1/_2（roi 由 [245,92,180,30] 拆为 [245,94,66,27] 与 [358,95,60,24]，各带点击点 target 193,74 / 304,74）；「商店」RTF_GOshop 拆为 RTF_GOshop_1/_2（roi [231,226,57,29] 与 [345,228,51,26]）；GetDaily_RTF / RTF_EnterSquare / RTF_Start 三处 next 同步改为指向 _1/_2；</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>3.StartGame 启动链时序微调：BackHome pre_delay 与 post_delay 2s→1.5s；Cancle / GoBack / GoBack2 / PVPAward / RejectAward / RejectAnnouncement 的 post_delay 2s→3s；SevenDays post_delay 2s→1.5s；WhetherSevenDaysTick post_delay 1.5s→3s；ClickContinue2 新增 post_delay 9s（登录继续后等游戏起画面）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4.WarcraftShop 本版仅 MPE 元数据（savedViewport / lastSyncTime），无行为改动；</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>5.已知遗留（沿用 v26.10.8）：RTF_OnSquare_1/_2 与 EnterWarcraft_WS 的 next 自引用重试均未设 max_hit；RTF_GOshop_1/_2 已不再是自引用。</t>
         </is>
       </c>
     </row>
